--- a/Energy/A2_Extra_Inputs/A-Xtra_Emissions.xlsx
+++ b/Energy/A2_Extra_Inputs/A-Xtra_Emissions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Energy_19\A2_Extra_Inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Energy_20\A2_Extra_Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0278A48-F841-4F29-8E0F-4C057C985133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87559DF7-0F8F-418E-81D0-55DA18751B20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GHGs" sheetId="1" r:id="rId1"/>
@@ -4887,8 +4887,8 @@
         <v>111</v>
       </c>
       <c r="C252" s="52">
-        <f>C203</f>
-        <v>3.0000000000000001E-6</v>
+        <f>C240</f>
+        <v>3.8999999999999999E-6</v>
       </c>
       <c r="D252" t="s">
         <v>107</v>
@@ -4902,8 +4902,8 @@
         <v>111</v>
       </c>
       <c r="C253" s="52">
-        <f>C208</f>
-        <v>3.0000000000000001E-6</v>
+        <f>C241</f>
+        <v>3.3000000000000003E-5</v>
       </c>
       <c r="D253" t="s">
         <v>107</v>
@@ -5806,8 +5806,8 @@
         <v>112</v>
       </c>
       <c r="C314" s="52">
-        <f>C265</f>
-        <v>5.9999999999999997E-7</v>
+        <f>C302</f>
+        <v>3.8999999999999999E-6</v>
       </c>
       <c r="D314" t="s">
         <v>113</v>
@@ -5821,8 +5821,8 @@
         <v>112</v>
       </c>
       <c r="C315" s="52">
-        <f>C270</f>
-        <v>5.9999999999999997E-7</v>
+        <f>C303</f>
+        <v>3.2000000000000003E-6</v>
       </c>
       <c r="D315" t="s">
         <v>113</v>
@@ -6080,8 +6080,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B8F814574E960A4499025803604D4DF4" ma:contentTypeVersion="9" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="613b0908c48a25395136f5b5d1e9264a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b2ff61d-e0c4-454b-ba72-44cf85c32a41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f5652efc65d8021725ff526b59607fd6" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B8F814574E960A4499025803604D4DF4" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="314e7041d7d1561dbe33e80becf1c782">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b2ff61d-e0c4-454b-ba72-44cf85c32a41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="84c838da6aa04a0f137f8b0aba02cfe1" ns2:_="">
     <xsd:import namespace="4b2ff61d-e0c4-454b-ba72-44cf85c32a41"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -6159,8 +6159,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -6265,21 +6265,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C882E70A-B240-40D9-8363-7A3098F40C6F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4b2ff61d-e0c4-454b-ba72-44cf85c32a41"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E5AD284-FF35-4109-B9B0-65C74A9F973D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
